--- a/test/fixtures/Config_InvalidNames.xlsx
+++ b/test/fixtures/Config_InvalidNames.xlsx
@@ -12,6 +12,7 @@
     <sheet name="!!!" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="my-section" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="My Section" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Bad Assets!" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,4 +687,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>OrchestratorAssetFolder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ValueType</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>user.cred</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cred_sap_invalid</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SAP credential.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>queue#name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>queue_invalid</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Queue name asset.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>